--- a/StructureDefinition-heartland-risk-assessment.xlsx
+++ b/StructureDefinition-heartland-risk-assessment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-risk-assessment</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-risk-assessment</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -694,7 +694,7 @@
     <t>RiskAssessment.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient|Patient)
+    <t xml:space="preserve">Reference(https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient|Patient)
 </t>
   </si>
   <si>
@@ -967,7 +967,7 @@
     <t>Indicates how likely the outcome is (in the specified timeframe), expressed as a qualitative value (e.g. low, medium, or high).</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-risk-tier-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-risk-tier-vs</t>
   </si>
   <si>
     <t>RiskAssessment.prediction.relativeRisk</t>
@@ -1402,7 +1402,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.47265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.8828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.1015625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.91015625" customWidth="true" bestFit="true"/>
